--- a/reports/excel/Mobile_E2E_Report.xlsx
+++ b/reports/excel/Mobile_E2E_Report.xlsx
@@ -97,7 +97,7 @@
     <t>PASSED</t>
   </si>
   <si>
-    <t>2026-08-20 03:51:22</t>
+    <t>2026-08-20 04:37:21</t>
   </si>
   <si>
     <t>TC-APP-002</t>

--- a/reports/excel/Mobile_E2E_Report.xlsx
+++ b/reports/excel/Mobile_E2E_Report.xlsx
@@ -97,7 +97,7 @@
     <t>PASSED</t>
   </si>
   <si>
-    <t>2026-08-20 04:37:21</t>
+    <t>2026-08-20 03:51:22</t>
   </si>
   <si>
     <t>TC-APP-002</t>

--- a/reports/excel/Mobile_E2E_Report.xlsx
+++ b/reports/excel/Mobile_E2E_Report.xlsx
@@ -97,7 +97,7 @@
     <t>PASSED</t>
   </si>
   <si>
-    <t>2026-08-20 03:51:22</t>
+    <t>2026-08-20 04:41:24</t>
   </si>
   <si>
     <t>TC-APP-002</t>

--- a/reports/excel/Mobile_E2E_Report.xlsx
+++ b/reports/excel/Mobile_E2E_Report.xlsx
@@ -97,7 +97,7 @@
     <t>PASSED</t>
   </si>
   <si>
-    <t>2026-08-20 04:41:24</t>
+    <t>2026-08-20 03:51:22</t>
   </si>
   <si>
     <t>TC-APP-002</t>
